--- a/artfynd/A 62118-2023 artfynd.xlsx
+++ b/artfynd/A 62118-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 62118-2023 artfynd.xlsx
+++ b/artfynd/A 62118-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -935,6 +935,822 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>114896118</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57252</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bengtmyren (Sakrisbodarna, Ås), Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>478258</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7019898</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-02-27</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-02-27</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>114895989</v>
+      </c>
+      <c r="B5" t="n">
+        <v>78454</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bengtmyren (Bengtmyren), Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>478215</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7019904</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-02-27</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-02-27</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>114895979</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79411</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bengtmyren (Bengtmyren), Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>478224</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7019900</v>
+      </c>
+      <c r="S6" t="n">
+        <v>20</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-02-27</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-02-27</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Stort antal bålar på aspar i området.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>114896301</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57385</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bengtmyren (Sakrisbodarna, Ås), Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>478261</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7019899</v>
+      </c>
+      <c r="S7" t="n">
+        <v>50</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-02-27</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-02-27</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>114896194</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79411</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bengtmyren (Bengtmyren), Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>478257</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7019903</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-02-27</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-02-27</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt på äldre asp tillsammans med lunglav.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>114896058</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79505</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bengtmyren (Bengtmyren), Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>478238</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7019888</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-02-27</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-02-27</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>114896183</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79505</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bengtmyren (Bengtmyren), Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>478257</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7019899</v>
+      </c>
+      <c r="S10" t="n">
+        <v>50</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-02-27</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-02-27</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rikligt med bålar på sälg, asp och även granar intill dessa.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 62118-2023 artfynd.xlsx
+++ b/artfynd/A 62118-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1751,6 +1751,103 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128139022</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Borggrensvikens naturreservat, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>478512</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7019969</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 62118-2023 artfynd.xlsx
+++ b/artfynd/A 62118-2023 artfynd.xlsx
@@ -1756,7 +1756,7 @@
         <v>128139022</v>
       </c>
       <c r="B11" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 62118-2023 artfynd.xlsx
+++ b/artfynd/A 62118-2023 artfynd.xlsx
@@ -1756,7 +1756,7 @@
         <v>128139022</v>
       </c>
       <c r="B11" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 62118-2023 artfynd.xlsx
+++ b/artfynd/A 62118-2023 artfynd.xlsx
@@ -1756,7 +1756,7 @@
         <v>128139022</v>
       </c>
       <c r="B11" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 62118-2023 artfynd.xlsx
+++ b/artfynd/A 62118-2023 artfynd.xlsx
@@ -1756,7 +1756,7 @@
         <v>128139022</v>
       </c>
       <c r="B11" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 62118-2023 artfynd.xlsx
+++ b/artfynd/A 62118-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1848,6 +1848,112 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129566659</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Borggrensviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>478493</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7020065</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 62118-2023 artfynd.xlsx
+++ b/artfynd/A 62118-2023 artfynd.xlsx
@@ -1853,7 +1853,7 @@
         <v>129566659</v>
       </c>
       <c r="B12" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 62118-2023 artfynd.xlsx
+++ b/artfynd/A 62118-2023 artfynd.xlsx
@@ -1853,7 +1853,7 @@
         <v>129566659</v>
       </c>
       <c r="B12" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 62118-2023 artfynd.xlsx
+++ b/artfynd/A 62118-2023 artfynd.xlsx
@@ -1853,7 +1853,7 @@
         <v>129566659</v>
       </c>
       <c r="B12" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 62118-2023 artfynd.xlsx
+++ b/artfynd/A 62118-2023 artfynd.xlsx
@@ -1853,7 +1853,7 @@
         <v>129566659</v>
       </c>
       <c r="B12" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 62118-2023 artfynd.xlsx
+++ b/artfynd/A 62118-2023 artfynd.xlsx
@@ -1853,7 +1853,7 @@
         <v>129566659</v>
       </c>
       <c r="B12" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 62118-2023 artfynd.xlsx
+++ b/artfynd/A 62118-2023 artfynd.xlsx
@@ -1853,7 +1853,7 @@
         <v>129566659</v>
       </c>
       <c r="B12" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 62118-2023 artfynd.xlsx
+++ b/artfynd/A 62118-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,64 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3036421</v>
+        <v>231363</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98056</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>167</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Höstlåsbräken</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Botrychium multifidum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(S. G. Gmel.) Rupr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Borggrensviken - Sågbäcken, Jmt</t>
+          <t>Kraftledningsgata Hismmofors-Nyvik, Ö om Patronbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478488.5870879884</v>
+        <v>478325</v>
       </c>
       <c r="R2" t="n">
-        <v>7020060.343414153</v>
+        <v>7019783</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,27 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2010-08-14</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1993-08-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2010-08-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1993-08-07</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Granskog i sluttning. Grusås.</t>
+          <t>Sten Olofsson</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -793,73 +764,66 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Granskog på grusås</t>
+          <t>Artificiell miljö</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>Staffan Åström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>Staffan Åström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>62055219</v>
+        <v>231364</v>
       </c>
       <c r="B3" t="n">
-        <v>89952</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98056</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>760</v>
+        <v>167</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Höstlåsbräken</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Botrychium multifidum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(S. G. Gmel.) Rupr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Borggrensviken - Sågbäcken, Jmt</t>
+          <t>Tängskogen: Kraftledningen_1, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478143.8096091508</v>
+        <v>478305</v>
       </c>
       <c r="R3" t="n">
-        <v>7019875.177072824</v>
+        <v>7019787</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -884,29 +848,24 @@
           <t>Ås</t>
         </is>
       </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Z-Kro-0182</t>
+        </is>
+      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>1990-01-01</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1993-08-07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1999-12-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1993-08-07</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Uppgiftslämnare; SNF Krokomskretsen Tängskogen, ca 25 m norr om kraftledningen, ca 600 m nordost om Patronbodarna, inom fastigheten Täng 1:7,</t>
+          <t>Sten Olofsson</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -921,75 +880,64 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>Z Län Floraväktarna</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Lars-Åke Bäckström</t>
+          <t>Sten Olofsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>Lst Z Artdatabas</t>
+          <t>Floraväkteri Sverige</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>114896301</v>
+        <v>68149510</v>
       </c>
       <c r="B4" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>504</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bengtmyren (Sakrisbodarna, Ås), Jmt</t>
+          <t>Bengtmyren, Täng, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478262</v>
+        <v>478331</v>
       </c>
       <c r="R4" t="n">
-        <v>7019899</v>
+        <v>7019896</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1011,24 +959,24 @@
           <t>Ås</t>
         </is>
       </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Z-Kro-1270</t>
+        </is>
+      </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-02-27</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>11:46</t>
+          <t>1980-01-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-02-27</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>11:46</t>
+          <t>1989-12-31</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Bengtmyren, västra delen, (Tängskogen). Koordinat O1438055, N7022655 (±10m). Kopia till floraväkteriet.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1043,71 +991,64 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Lars-Åke Bäckström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Åke Jonsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>114896118</v>
+        <v>62055219</v>
       </c>
       <c r="B5" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92509</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>760</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bengtmyren (Sakrisbodarna, Ås), Jmt</t>
+          <t>Borggrensviken - Sågbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478257</v>
+        <v>478144</v>
       </c>
       <c r="R5" t="n">
-        <v>7019897</v>
+        <v>7019875</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1131,22 +1072,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-02-27</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>11:35</t>
+          <t>1990-01-01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-02-27</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>11:35</t>
+          <t>1999-12-31</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Uppgiftslämnare; SNF Krokomskretsen Tängskogen, ca 25 m norr om kraftledningen, ca 600 m nordost om Patronbodarna, inom fastigheten Täng 1:7,</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1161,66 +1097,65 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Lars-Åke Bäckström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Via Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Lst Z Artdatabas</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>114896194</v>
+        <v>114895989</v>
       </c>
       <c r="B6" t="n">
-        <v>79464</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bengtmyren (Bengtmyren), Jmt</t>
+          <t>Bengtmyren, Bengtmyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478258</v>
+        <v>478215</v>
       </c>
       <c r="R6" t="n">
-        <v>7019902</v>
+        <v>7019904</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1249,7 +1184,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1259,12 +1194,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:42</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Rikligt på äldre asp tillsammans med lunglav.</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1294,12 +1224,7 @@
         <v>114895979</v>
       </c>
       <c r="B7" t="n">
-        <v>79464</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1328,7 +1253,7 @@
       <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bengtmyren (Bengtmyren), Jmt</t>
+          <t>Bengtmyren, Bengtmyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
@@ -1409,54 +1334,49 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>114895989</v>
+        <v>114896194</v>
       </c>
       <c r="B8" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bengtmyren (Bengtmyren), Jmt</t>
+          <t>Bengtmyren, Bengtmyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478215</v>
+        <v>478258</v>
       </c>
       <c r="R8" t="n">
-        <v>7019904</v>
+        <v>7019902</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1485,7 +1405,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1495,7 +1415,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt på äldre asp tillsammans med lunglav.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1525,12 +1450,7 @@
         <v>114896058</v>
       </c>
       <c r="B9" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1479,7 @@
       <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bengtmyren (Bengtmyren), Jmt</t>
+          <t>Bengtmyren, Bengtmyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
@@ -1638,12 +1558,7 @@
         <v>114896183</v>
       </c>
       <c r="B10" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1672,7 +1587,7 @@
       <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bengtmyren (Bengtmyren), Jmt</t>
+          <t>Bengtmyren, Bengtmyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
@@ -1753,48 +1668,54 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128139022</v>
+        <v>114896118</v>
       </c>
       <c r="B11" t="n">
-        <v>98592</v>
+        <v>57950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Borggrensvikens naturreservat, Jmt</t>
+          <t>Bengtmyren, Sakrisbodarna, Ås, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478512</v>
+        <v>478257</v>
       </c>
       <c r="R11" t="n">
-        <v>7019969</v>
+        <v>7019897</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1818,12 +1739,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2024-02-27</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2024-02-27</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1838,12 +1769,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1853,7 +1784,7 @@
         <v>129566659</v>
       </c>
       <c r="B12" t="n">
-        <v>57826</v>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1954,6 +1885,654 @@
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129566669</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Borggrensviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>478582</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7020099</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>86340016</v>
+      </c>
+      <c r="B14" t="n">
+        <v>43249</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>101248</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Violett guldvinge</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lycaena helle</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Bakut, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>478110</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7019849</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2020-06-18</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2020-06-18</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>86340037</v>
+      </c>
+      <c r="B15" t="n">
+        <v>43249</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>101248</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Violett guldvinge</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lycaena helle</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Bakut, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>478227</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7019818</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2020-06-18</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2020-06-18</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>114896301</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Bengtmyren, Sakrisbodarna, Ås, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>478262</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7019899</v>
+      </c>
+      <c r="S16" t="n">
+        <v>50</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-02-27</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-02-27</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>3036421</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Borggrensviken - Sågbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>478489</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7020060</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2010-08-14</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2010-08-14</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Granskog i sluttning. Grusås.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Granskog på grusås</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128139022</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Borggrensvikens naturreservat, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>478512</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7019969</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ås</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-08-17</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 62118-2023 artfynd.xlsx
+++ b/artfynd/A 62118-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/231363</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -893,6 +903,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/231364</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1004,6 +1019,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68149510</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1110,6 +1130,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62055219</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1218,6 +1243,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114895989</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1331,6 +1361,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114895979</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1444,6 +1479,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114896194</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1552,6 +1592,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114896058</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1665,6 +1710,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114896183</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1778,6 +1828,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114896118</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1884,6 +1939,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129566659</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1990,6 +2050,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129566669</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2093,6 +2158,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86340016</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2196,6 +2266,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86340037</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2309,6 +2384,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114896301</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2435,6 +2515,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3036421</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2532,8 +2617,32 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128139022</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>